--- a/MU/Test upload format/SHG/2025 - 2026 -SHG/CP1 25-26.xlsx
+++ b/MU/Test upload format/SHG/2025 - 2026 -SHG/CP1 25-26.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="62">
   <si>
     <t>custid</t>
   </si>
@@ -86,40 +86,133 @@
     <t>modifiedloancat</t>
   </si>
   <si>
-    <t>cust01</t>
-  </si>
-  <si>
-    <t>cust01AC01new</t>
+    <t>HomeStay</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252601</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>01-04-2025</t>
+  </si>
+  <si>
+    <t>1000001</t>
+  </si>
+  <si>
+    <t>SHG</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252602</t>
   </si>
   <si>
     <t>10000</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>40000</t>
-  </si>
-  <si>
-    <t>01-04-2025</t>
-  </si>
-  <si>
-    <t>2000001</t>
+    <t>1000002</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252603</t>
+  </si>
+  <si>
+    <t>100</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
-    <t>TP</t>
-  </si>
-  <si>
-    <t>cust06</t>
-  </si>
-  <si>
-    <t>cust01AC06new</t>
-  </si>
-  <si>
-    <t>1900001</t>
+    <t>01-04-2026</t>
+  </si>
+  <si>
+    <t>1000003</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252604</t>
+  </si>
+  <si>
+    <t>1000004</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252605</t>
+  </si>
+  <si>
+    <t>1000005</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252606</t>
+  </si>
+  <si>
+    <t>1000006</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252607</t>
+  </si>
+  <si>
+    <t>1000007</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252608</t>
+  </si>
+  <si>
+    <t>1000008</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252609</t>
+  </si>
+  <si>
+    <t>1000009</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252610</t>
+  </si>
+  <si>
+    <t>1000010</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252611</t>
+  </si>
+  <si>
+    <t>1000011</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252612</t>
+  </si>
+  <si>
+    <t>1000012</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252613</t>
+  </si>
+  <si>
+    <t>1000013</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252614</t>
+  </si>
+  <si>
+    <t>1000014</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252615</t>
+  </si>
+  <si>
+    <t>1000015</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252616</t>
+  </si>
+  <si>
+    <t>1000016</t>
+  </si>
+  <si>
+    <t>CR14Q1SHG252617</t>
+  </si>
+  <si>
+    <t>1000017</t>
   </si>
 </sst>
 </file>
@@ -132,7 +225,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,6 +242,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -493,39 +592,11 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -645,156 +716,157 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1114,69 +1186,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
+  <dimension ref="A1:T18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.8571428571429" customWidth="1"/>
-    <col min="2" max="2" width="24.5714285714286" customWidth="1"/>
-    <col min="3" max="3" width="15.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="11.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="20.5714285714286" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="10.8571428571429" customWidth="1"/>
-    <col min="9" max="9" width="13.5714285714286" customWidth="1"/>
-    <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="15.8571428571429" customWidth="1"/>
-    <col min="13" max="13" width="18.5714285714286" customWidth="1"/>
-    <col min="14" max="14" width="17.2857142857143" customWidth="1"/>
-    <col min="15" max="15" width="13.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="17.8571428571429" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5714285714286" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.2857142857143" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5714285714286" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5714285714286" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.8571428571429" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5714285714286" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="1"/>
+    <col min="11" max="11" width="17" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.8571428571429" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5714285714286" style="1" customWidth="1"/>
+    <col min="14" max="14" width="17.2857142857143" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.2857142857143" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:20">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="5" t="s">
@@ -1188,106 +1262,810 @@
       <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" customFormat="1" spans="1:19">
+    <row r="2" s="1" customFormat="1" spans="1:20">
       <c r="A2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="6" t="s">
+      <c r="D2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="9"/>
+      <c r="F2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11">
+        <v>1</v>
+      </c>
+      <c r="K2" s="11">
+        <v>1</v>
+      </c>
+      <c r="L2" s="11">
+        <v>1</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="9"/>
-      <c r="J2"/>
-      <c r="K2" s="9">
-        <v>1</v>
-      </c>
-      <c r="L2" s="9">
-        <v>1</v>
-      </c>
-      <c r="M2" s="10" t="s">
+      <c r="N2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2"/>
-      <c r="P2" t="s">
+      <c r="T2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="B3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="R2" t="s">
-        <v>22</v>
-      </c>
-      <c r="S2" t="s">
+      <c r="C3" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>27</v>
       </c>
+      <c r="G3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="11">
+        <v>1</v>
+      </c>
+      <c r="K3" s="11">
+        <v>1</v>
+      </c>
+      <c r="L3" s="11">
+        <v>1</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="3" spans="1:19">
-      <c r="A3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="6" t="s">
+    <row r="4" spans="1:20">
+      <c r="A4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="B4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="9">
-        <v>1</v>
-      </c>
-      <c r="L3" s="9">
-        <v>1</v>
-      </c>
-      <c r="M3" s="10" t="s">
+      <c r="G4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="11">
+        <v>1</v>
+      </c>
+      <c r="K4" s="11">
+        <v>1</v>
+      </c>
+      <c r="L4" s="11">
+        <v>1</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="11">
+        <v>1</v>
+      </c>
+      <c r="K5" s="11">
+        <v>1</v>
+      </c>
+      <c r="L5" s="11">
+        <v>1</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="11">
+        <v>1</v>
+      </c>
+      <c r="K6" s="11">
+        <v>1</v>
+      </c>
+      <c r="L6" s="11">
+        <v>1</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>26</v>
-      </c>
-      <c r="R3" t="s">
-        <v>22</v>
-      </c>
-      <c r="S3" t="s">
+      <c r="D7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="11">
+        <v>1</v>
+      </c>
+      <c r="K7" s="11">
+        <v>1</v>
+      </c>
+      <c r="L7" s="11">
+        <v>1</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>27</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="11">
+        <v>1</v>
+      </c>
+      <c r="K8" s="11">
+        <v>1</v>
+      </c>
+      <c r="L8" s="11">
+        <v>1</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="11">
+        <v>1</v>
+      </c>
+      <c r="K9" s="11">
+        <v>1</v>
+      </c>
+      <c r="L9" s="11">
+        <v>1</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="11">
+        <v>1</v>
+      </c>
+      <c r="K10" s="11">
+        <v>1</v>
+      </c>
+      <c r="L10" s="11">
+        <v>1</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="11">
+        <v>1</v>
+      </c>
+      <c r="K11" s="11">
+        <v>1</v>
+      </c>
+      <c r="L11" s="11">
+        <v>1</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="11">
+        <v>1</v>
+      </c>
+      <c r="K12" s="11">
+        <v>1</v>
+      </c>
+      <c r="L12" s="11">
+        <v>1</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="11">
+        <v>1</v>
+      </c>
+      <c r="K13" s="11">
+        <v>1</v>
+      </c>
+      <c r="L13" s="11">
+        <v>1</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="7">
+        <v>10000</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" s="11">
+        <v>1</v>
+      </c>
+      <c r="K14" s="11">
+        <v>1</v>
+      </c>
+      <c r="L14" s="11">
+        <v>1</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="N14" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="11">
+        <v>1</v>
+      </c>
+      <c r="K15" s="11">
+        <v>1</v>
+      </c>
+      <c r="L15" s="11">
+        <v>1</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1000</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" s="11">
+        <v>1</v>
+      </c>
+      <c r="K16" s="11">
+        <v>1</v>
+      </c>
+      <c r="L16" s="11">
+        <v>1</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
+      <c r="A17" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" s="11">
+        <v>1</v>
+      </c>
+      <c r="K17" s="11">
+        <v>1</v>
+      </c>
+      <c r="L17" s="11">
+        <v>1</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="N17" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="7">
+        <v>10000</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="11">
+        <v>1</v>
+      </c>
+      <c r="K18" s="11">
+        <v>1</v>
+      </c>
+      <c r="L18" s="11">
+        <v>1</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="N18" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
